--- a/artfynd/A 52601-2024 artfynd.xlsx
+++ b/artfynd/A 52601-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121853419</v>
       </c>
       <c r="B2" t="n">
-        <v>90748</v>
+        <v>90762</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 52601-2024 artfynd.xlsx
+++ b/artfynd/A 52601-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121853419</v>
       </c>
       <c r="B2" t="n">
-        <v>90762</v>
+        <v>90764</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 52601-2024 artfynd.xlsx
+++ b/artfynd/A 52601-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121853419</v>
       </c>
       <c r="B2" t="n">
-        <v>90764</v>
+        <v>90765</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 52601-2024 artfynd.xlsx
+++ b/artfynd/A 52601-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121853419</v>
       </c>
       <c r="B2" t="n">
-        <v>90765</v>
+        <v>90774</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 52601-2024 artfynd.xlsx
+++ b/artfynd/A 52601-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121853419</v>
+        <v>121853428</v>
       </c>
       <c r="B2" t="n">
-        <v>90799</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>533396</v>
+        <v>533547</v>
       </c>
       <c r="R2" t="n">
-        <v>6668430</v>
+        <v>6668464</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -769,7 +764,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>äldre blåbärstallskog</t>
+          <t>äldre tallskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -784,6 +779,1213 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>121853431</v>
+      </c>
+      <c r="B3" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Mellan Sarvtjärnen och Fågelleksmossen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>533534</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6668561</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Gysinge Skog naturvärdesbedömning.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>äldre tallskog</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>121853433</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Mellan Sarvtjärnen och Fågelleksmossen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>533641</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6668692</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Gysinge Skog naturvärdesbedömning.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>äldre blåbärsbarrblandskog</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121853409</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97358</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>53</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Mellan Sarvtjärnen och Fågelleksmossen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>533485</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6668453</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Gysinge Skog naturvärdesbedömning.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>äldre blåbärsbarrblandskog</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>barrträdslåga i fuktstråk</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121853419</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91930</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Mellan Sarvtjärnen och Fågelleksmossen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>533396</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6668430</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Gysinge Skog naturvärdesbedömning.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>äldre blåbärstallskog</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121853415</v>
+      </c>
+      <c r="B7" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Mellan Sarvtjärnen och Fågelleksmossen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>533294</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6668098</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Gysinge Skog naturvärdesbedömning.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>gammal hällmarkstallskog</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>121853418</v>
+      </c>
+      <c r="B8" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Mellan Sarvtjärnen och Fågelleksmossen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>533284</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6668118</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Gysinge Skog naturvärdesbedömning.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>gammal hällmarkstallskog</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>121853414</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Mellan Sarvtjärnen och Fågelleksmossen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>533294</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6668116</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Gysinge Skog naturvärdesbedömning.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>gammal hällmarkstallskog</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>liten silvervedsbit</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>121853421</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Mellan Sarvtjärnen och Fågelleksmossen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>533416</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6668382</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Gysinge Skog naturvärdesbedömning.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>äldre blåbärstallskog</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>torrtall</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>121853410</v>
+      </c>
+      <c r="B11" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Mellan Sarvtjärnen och Fågelleksmossen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>533416</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6668444</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Gysinge Skog naturvärdesbedömning.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>äldre blåbärsbarrblandskog</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>torrgran</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>121853411</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Mellan Sarvtjärnen och Fågelleksmossen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>533414</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6668444</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Gysinge Skog naturvärdesbedömning.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>äldre blåbärsbarrblandskog</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>121853420</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Mellan Sarvtjärnen och Fågelleksmossen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>533402</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6668416</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Gysinge Skog naturvärdesbedömning.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>äldre blåbärstallskog</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 52601-2024 artfynd.xlsx
+++ b/artfynd/A 52601-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121853428</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121853431</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121853433</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121853415</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121853418</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1319,6 +1349,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121853414</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1431,6 +1466,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121853409</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1538,6 +1578,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121853419</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1655,6 +1700,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121853421</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1772,6 +1822,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121853410</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1879,6 +1934,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121853411</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1986,8 +2046,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121853420</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>